--- a/Перечень_должностей_ИОТ_ШР_20.10.2026.xlsx
+++ b/Перечень_должностей_ИОТ_ШР_20.10.2026.xlsx
@@ -11313,17 +11313,22 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I213" s="4" t="inlineStr">
@@ -11331,10 +11336,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11411,17 +11420,22 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr">
@@ -11429,10 +11443,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11509,17 +11527,22 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I217" s="4" t="inlineStr">
@@ -11527,10 +11550,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J217" s="4" t="inlineStr"/>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11558,17 +11585,22 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I218" s="4" t="inlineStr">
@@ -11576,10 +11608,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J218" s="4" t="inlineStr"/>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11607,17 +11643,22 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr">
@@ -11625,10 +11666,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J219" s="4" t="inlineStr"/>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11760,17 +11805,22 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I222" s="4" t="inlineStr">
@@ -11778,10 +11828,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J222" s="4" t="inlineStr"/>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11809,17 +11863,22 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr">
@@ -11827,10 +11886,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J223" s="4" t="inlineStr"/>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11858,17 +11921,22 @@
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I224" s="4" t="inlineStr">
@@ -11876,10 +11944,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J224" s="4" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11910,17 +11982,22 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr">
@@ -11928,10 +12005,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J225" s="4" t="inlineStr"/>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -11959,17 +12040,22 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46 (новый) Линейные руководители производства</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ИОТ-01 – Общие требования по охране труда для работников, занятых в производстве
+ИОТ-90 – Инструкция по оказанию первой помощи пострадавшему
+ИОТ-103 – Инструкция по охране труда для работников, направляемых в служебную командировку
+ИОТ-109 – Инструкция по охране труда при передвижении (проезду) по территории производственных помещений (объектов)
+ИОТ-110 – Инструкция по охране труда при проведении культурно-массовых мероприятий
+ИОТ-125 – Инструкция по охране труда для руководителей и специалистов (п.1.2 – линейные руководители производства)</t>
         </is>
       </c>
       <c r="I226" s="4" t="inlineStr">
@@ -11977,10 +12063,14 @@
           <t>Нет в перечне (линейный руководитель)</t>
         </is>
       </c>
-      <c r="J226" s="4" t="inlineStr"/>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t>ИОТ-125 распространена 21.10.2026</t>
+        </is>
+      </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>Линейный руководитель производства. Решение: отдельный пункт «Руководители производственных подразделений» (ИОТ-01, 125 + ИОТ профессий участка) или п.45.</t>
+          <t>Решение 21.10.2026: ИОТ-125 распространена на линейных руководителей производства. Добавить в перечень п.46 и разработать программу; ИОТ по видам работ – по матрице.</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14985,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -14925,7 +15015,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -15385,7 +15475,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -15835,7 +15925,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -15865,7 +15955,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -16063,7 +16153,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -20579,7 +20669,7 @@
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
@@ -20833,7 +20923,7 @@
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -20919,7 +21009,7 @@
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
@@ -20949,7 +21039,7 @@
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
@@ -21403,7 +21493,7 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
@@ -21909,7 +21999,7 @@
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
@@ -22471,7 +22561,7 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F353" s="4" t="inlineStr">
@@ -22585,7 +22675,7 @@
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F357" s="4" t="inlineStr">
@@ -22729,7 +22819,7 @@
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
@@ -22759,7 +22849,7 @@
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
@@ -22995,7 +23085,7 @@
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F371" s="4" t="inlineStr">
@@ -23081,7 +23171,7 @@
       </c>
       <c r="E374" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F374" s="4" t="inlineStr">
@@ -23559,7 +23649,7 @@
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>Программа отсутствует</t>
+          <t>Разработать</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
